--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>Source</t>
+  </si>
+  <si>
+    <t>Link</t>
   </si>
 </sst>
 </file>
@@ -387,10 +390,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,6 +435,9 @@
       </c>
       <c r="N1" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2914" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2948" uniqueCount="30">
   <si>
     <t>ID</t>
   </si>
@@ -92,6 +92,18 @@
   </si>
   <si>
     <t>Dawes Rolls Full Document - Choctaw By Blood - Page 168</t>
+  </si>
+  <si>
+    <t>Stricken from roll</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Image Name</t>
+  </si>
+  <si>
+    <t>Image Binary</t>
   </si>
 </sst>
 </file>
@@ -423,15 +435,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O1446"/>
+  <dimension ref="A1:Q1446"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="22.42578125" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" customWidth="1"/>
     <col min="12" max="12" width="17.42578125" customWidth="1"/>
     <col min="14" max="14" width="54.42578125" customWidth="1"/>
+    <col min="16" max="16" width="16.28515625" customWidth="1"/>
+    <col min="17" max="17" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,8 +492,14 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1</v>
       </c>
@@ -495,7 +516,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:17">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -515,7 +536,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:17">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -535,7 +556,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:17">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -555,7 +576,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:17">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -575,7 +596,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:17">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -595,7 +616,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:17">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -615,7 +636,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:17">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -635,7 +656,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:17">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -655,7 +676,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:17">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -675,7 +696,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:17">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -695,7 +716,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:17">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -715,7 +736,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:17">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -735,7 +756,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:17">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -755,7 +776,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:17">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -8863,8 +8884,35 @@
         <f t="shared" si="21"/>
         <v>162</v>
       </c>
+      <c r="D421" t="s">
+        <v>26</v>
+      </c>
+      <c r="E421" t="s">
+        <v>27</v>
+      </c>
+      <c r="F421" t="s">
+        <v>27</v>
+      </c>
+      <c r="G421" t="s">
+        <v>27</v>
+      </c>
+      <c r="H421">
+        <v>-1</v>
+      </c>
+      <c r="I421" t="s">
+        <v>27</v>
+      </c>
+      <c r="J421" t="s">
+        <v>27</v>
+      </c>
+      <c r="K421" t="s">
+        <v>27</v>
+      </c>
       <c r="L421" t="s">
-        <v>15</v>
+        <v>27</v>
+      </c>
+      <c r="M421" t="s">
+        <v>27</v>
       </c>
       <c r="N421" t="str">
         <f t="shared" si="22"/>
@@ -22655,8 +22703,35 @@
         <f t="shared" si="55"/>
         <v>166</v>
       </c>
+      <c r="D1111" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1111" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1111" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1111" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1111">
+        <v>-1</v>
+      </c>
+      <c r="I1111" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1111" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1111" t="s">
+        <v>27</v>
+      </c>
       <c r="L1111" t="s">
-        <v>15</v>
+        <v>27</v>
+      </c>
+      <c r="M1111" t="s">
+        <v>27</v>
       </c>
       <c r="N1111" t="str">
         <f t="shared" si="56"/>
@@ -22675,8 +22750,35 @@
         <f t="shared" si="55"/>
         <v>166</v>
       </c>
+      <c r="D1112" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1112" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1112" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1112">
+        <v>-1</v>
+      </c>
+      <c r="I1112" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1112" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1112" t="s">
+        <v>27</v>
+      </c>
       <c r="L1112" t="s">
-        <v>15</v>
+        <v>27</v>
+      </c>
+      <c r="M1112" t="s">
+        <v>27</v>
       </c>
       <c r="N1112" t="str">
         <f t="shared" si="56"/>
@@ -22695,8 +22797,35 @@
         <f t="shared" si="55"/>
         <v>166</v>
       </c>
+      <c r="D1113" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1113" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1113" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1113" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1113">
+        <v>-1</v>
+      </c>
+      <c r="I1113" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1113" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1113" t="s">
+        <v>27</v>
+      </c>
       <c r="L1113" t="s">
-        <v>15</v>
+        <v>27</v>
+      </c>
+      <c r="M1113" t="s">
+        <v>27</v>
       </c>
       <c r="N1113" t="str">
         <f t="shared" si="56"/>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2948" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2949" uniqueCount="31">
   <si>
     <t>ID</t>
   </si>
@@ -100,10 +100,13 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Image Name</t>
+    <t>ImageName</t>
   </si>
   <si>
-    <t>Image Binary</t>
+    <t>ImageBinary</t>
+  </si>
+  <si>
+    <t>TribeRelationship</t>
   </si>
 </sst>
 </file>
@@ -435,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q1446"/>
+  <dimension ref="A1:R1446"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="22.42578125" customWidth="1"/>
@@ -444,9 +447,10 @@
     <col min="14" max="14" width="54.42578125" customWidth="1"/>
     <col min="16" max="16" width="16.28515625" customWidth="1"/>
     <col min="17" max="17" width="13.85546875" customWidth="1"/>
+    <col min="18" max="18" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,8 +502,11 @@
       <c r="Q1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1</v>
       </c>
@@ -516,7 +523,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -536,7 +543,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -556,7 +563,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -576,7 +583,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -596,7 +603,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -616,7 +623,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -636,7 +643,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -656,7 +663,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -676,7 +683,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -696,7 +703,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -716,7 +723,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -736,7 +743,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -756,7 +763,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -776,7 +783,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 160</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
